--- a/cleaned_orders/cleaned_跨7.xlsx
+++ b/cleaned_orders/cleaned_跨7.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,35 +439,40 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>标准佣金率</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>店铺</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>内容形式</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>订单状态</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>SKU后四位</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>产品名称</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>标准佣金率</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>店铺</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>内容形式</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>订单状态</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>负责人</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>SourceID</t>
         </is>
@@ -481,11 +486,13 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -494,35 +501,40 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>跨7</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1372</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>洗护套装</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>跨7</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>视频</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>未匹配负责人</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -532,11 +544,13 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -545,35 +559,40 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>跨7</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1372</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>洗护套装</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>跨7</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>视频</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Lauren 美区</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>NzY0NzM3MDE4ODQ4ODQ5NDA0NjpkYW5pZWxhY2FicmVyYTAyMjg6MTQyMDU1YzE4MGNmNzMxNTgxMjFlYWMwOWQ2YWRmZjA6MQ==</t>
         </is>
@@ -587,11 +606,13 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -600,35 +621,40 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>跨7</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5692</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>洗发水买一送一</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>跨7</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>视频</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>媚跨境店</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>NzY0NzM3MDE4ODQ4ODQ5NDA0NjplbGJhaDEyOjEyMWNhZDc2ZjU1NjU3ZjBjNWE4MTFiZmVlY2NkZTI2OjE=</t>
         </is>
@@ -642,11 +668,13 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -655,35 +683,40 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>跨7</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5692</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>洗发水买一送一</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>跨7</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>视频</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>媚跨境店</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>NzY0NzM3MDE4ODQ4ODQ5NDA0NjplbGJhaDEyOjEyMWNhZDc2ZjU1NjU3ZjBjNWE4MTFiZmVlY2NkZTI2OjE=</t>
         </is>
@@ -697,11 +730,13 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -710,35 +745,40 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>跨7</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5692</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>洗发水买一送一</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>跨7</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>视频</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>媚跨境店</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>NzY0NzM3MDE4ODQ4ODQ5NDA0NjplbGJhaDEyOjEyMWNhZDc2ZjU1NjU3ZjBjNWE4MTFiZmVlY2NkZTI2OjE=</t>
         </is>
@@ -752,11 +792,13 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -765,35 +807,40 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>跨7</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5692</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>洗发水买一送一</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>跨7</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>视频</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>媚跨境店</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>NzY0NzM3MDE4ODQ4ODQ5NDA0NjplbGJhaDEyOjEyMWNhZDc2ZjU1NjU3ZjBjNWE4MTFiZmVlY2NkZTI2OjE=</t>
         </is>
@@ -807,11 +854,13 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -820,35 +869,40 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>跨7</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5692</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>洗发水买一送一</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>跨7</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>视频</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>媚跨境店</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>NzY0NzM3MDE4ODQ4ODQ5NDA0NjplbGJhaDEyOjEyMWNhZDc2ZjU1NjU3ZjBjNWE4MTFiZmVlY2NkZTI2OjE=</t>
         </is>
@@ -862,11 +916,13 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -875,35 +931,40 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>跨7</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5692</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>洗发水买一送一</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>跨7</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>视频</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>媚跨境店</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>NzY0NzM3MDE4ODQ4ODQ5NDA0NjplbGJhaDEyOjEyMWNhZDc2ZjU1NjU3ZjBjNWE4MTFiZmVlY2NkZTI2OjE=</t>
         </is>
@@ -917,11 +978,13 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -930,35 +993,40 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>跨7</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3484</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>洗发水精油</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>跨7</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>视频</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>媚跨境店</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>NzY0NzM3MDE4ODQ4ODQ5NDA0NjplbGJhaDEyOjEyMWNhZDc2ZjU1NjU3ZjBjNWE4MTFiZmVlY2NkZTI2OjE=</t>
         </is>
@@ -972,11 +1040,13 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -985,35 +1055,40 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>跨7</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4556</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>精油一瓶</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>跨7</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>视频</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>媚跨境店</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>NzY0NzM3MDE4ODQ4ODQ5NDA0NjplbGJhaDEyOjEyMWNhZDc2ZjU1NjU3ZjBjNWE4MTFiZmVlY2NkZTI2OjE=</t>
         </is>
@@ -1027,11 +1102,13 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026/6/4</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>1</v>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1040,35 +1117,40 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>跨7</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4556</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>精油一瓶</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>跨7</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>视频</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>媚跨境店</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>NzY0NzM3MDE4ODQ4ODQ5NDA0NjplbGJhaDEyOjEyMWNhZDc2ZjU1NjU3ZjBjNWE4MTFiZmVlY2NkZTI2OjE=</t>
         </is>
@@ -1082,11 +1164,13 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>1</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1095,35 +1179,40 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>跨7</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0700</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>洗发水</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>跨7</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>视频</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>小吴 美区旧版</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>NzY0NzM3MDE4ODQ4ODQ5NDA0NjplbGl6YWJldGhheWFsYTUwNDplZTY5MzE3NjMwZTZhMTZkNThmYjM2N2VlMTM1MjliMDox</t>
         </is>
@@ -1137,11 +1226,13 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1150,35 +1241,40 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>跨7</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1372</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>洗护套装</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>跨7</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>视频</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>宗跨境店</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>NzY0NzM3MDE4ODQ4ODQ5NDA0NjpmaW5kbG9vdDo0NGMzODMyMzE3NDkxN2UwOThlZmQ2YzQzM2M0ZTk1ODox</t>
         </is>
@@ -1192,11 +1288,13 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>1</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1205,35 +1303,40 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>跨7</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>9756</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>洗发水</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>跨7</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>视频</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>宗跨境店</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>NzY0NzM3MDE4ODQ4ODQ5NDA0NjpoYXBweXNob3A5Njg6MjRiZjMyZTdhMjljZWQ2OTNlZDRiNTcwZTA3YmI1ZDI6MQ==</t>
         </is>
@@ -1247,11 +1350,13 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1260,35 +1365,40 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>跨7</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>9756</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>洗发水</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>跨7</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>视频</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>宗跨境店</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>NzY0NzM3MDE4ODQ4ODQ5NDA0NjpoYXBweXNob3A5Njg6MjRiZjMyZTdhMjljZWQ2OTNlZDRiNTcwZTA3YmI1ZDI6MQ==</t>
         </is>
@@ -1302,11 +1412,13 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1315,35 +1427,40 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>跨7</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1372</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>洗护套装</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>跨7</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>视频</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>宗跨境店</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>NzY0NzM3MDE4ODQ4ODQ5NDA0NjpoYXBweXNob3A5Njg6MjRiZjMyZTdhMjljZWQ2OTNlZDRiNTcwZTA3YmI1ZDI6MQ==</t>
         </is>
@@ -1357,11 +1474,13 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>2</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1370,35 +1489,40 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>跨7</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0700</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>洗发水</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>22%</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>跨7</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>视频</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>小吴 美区旧版</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>NzY0NzM3MDE4ODQ4ODQ5NDA0Njpqb3JnZWdhbHZlemw6ZTI5ZGEwYzE0NTQyODI2MWZmODBjZDliZmM4MTQ1ZGI6MQ==</t>
         </is>
@@ -1412,11 +1536,13 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026/6/4</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1425,35 +1551,40 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>跨7</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0700</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>洗发水</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>22%</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>跨7</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>视频</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>小吴 美区旧版</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>NzY0NzM3MDE4ODQ4ODQ5NDA0Njpqb3JnZWdhbHZlemw6ZTI5ZGEwYzE0NTQyODI2MWZmODBjZDliZmM4MTQ1ZGI6MQ==</t>
         </is>
@@ -1467,11 +1598,13 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1480,35 +1613,40 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>跨7</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>商品橱窗</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0700</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>洗发水</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>15%</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>跨7</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>商品橱窗</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>未匹配负责人</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1518,11 +1656,13 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026/6/4</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1531,35 +1671,40 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>跨7</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1372</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
           <t>洗护套装</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>跨7</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>视频</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>宗跨境店</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>NzY0NzM3MDE4ODQ4ODQ5NDA0NjpsdWlzcnVpenBhejE3ODoxNmQ2MDVjZDMwNTQ0MWVkZjE4ZjgxMzhmMjA3MDlhZTox</t>
         </is>
@@ -1573,11 +1718,13 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>2</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1586,35 +1733,40 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>跨7</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>9756</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
           <t>洗发水</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>跨7</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>视频</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>媚跨境店</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>NzY0NzM3MDE4ODQ4ODQ5NDA0NjptYXJ0aGFfYnJpaTozYWZlNjZlOTM4OTZlYzg2ZGIyMmM5YTRlM2JkNTM5Njox</t>
         </is>
@@ -1628,11 +1780,13 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>2</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1641,35 +1795,40 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>跨7</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0700</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
           <t>洗发水</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>22%</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>跨7</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>视频</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>小吴 美区新版</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>NzY0NzM3MDE4ODQ4ODQ5NDA0Njpyb3NhLmZlcm5hbmRlejUxMjg6ZmM3MzRiZDJlNzU3OWEwNjUzYjk1MTMyNTc2ODk1ZmE6MQ==</t>
         </is>
@@ -1683,11 +1842,13 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026/6/3</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1696,35 +1857,40 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>跨7</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0700</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>洗发水</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>跨7</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>视频</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>Lauren 美区</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>NzY0NzM3MDE4ODQ4ODQ5NDA0Njp0b3J5MTUxODY6NDFmZGNkNDZhNmJjOThhYjgzMTE3NWZiYTk3ZjllYTc6MQ==</t>
         </is>
